--- a/artfynd/A 46157-2025 artfynd.xlsx
+++ b/artfynd/A 46157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174769</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129174780</v>
       </c>
       <c r="B3" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46157-2025 artfynd.xlsx
+++ b/artfynd/A 46157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174769</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129174780</v>
       </c>
       <c r="B3" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46157-2025 artfynd.xlsx
+++ b/artfynd/A 46157-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174769</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129174780</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46157-2025 artfynd.xlsx
+++ b/artfynd/A 46157-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129174769</v>
+        <v>129174655</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571865</v>
+        <v>571753</v>
       </c>
       <c r="R2" t="n">
-        <v>6414555</v>
+        <v>6414377</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,11 +757,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129174780</v>
+        <v>129174769</v>
       </c>
       <c r="B3" t="n">
-        <v>58100</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,16 +795,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,7 +817,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -866,6 +865,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,6 +891,111 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129174780</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 46157, Snärsfall, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571865</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6414555</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
